--- a/data/output/run-resume-2_Filled.xlsx
+++ b/data/output/run-resume-2_Filled.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "1. Access Control &amp; Identity - All production access requires Multi-Factor Authentication (MFA) via FIDO2 WebAuthn hardware keys or TOTP. SM")</t>
+          <t>Information_Security_Policy.md (quote: "## 1. Access Control &amp; Identity - All production access requires Multi-Factor Authentication (MFA) via FIDO2 WebAuthn hardware keys or TOTP.")</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "1. Access Control &amp; Identity - All production access requires Multi-Factor Authentication (MFA) via FIDO2 WebAuthn hardware keys or TOTP. SM")</t>
+          <t>Information_Security_Policy.md (quote: "## 1. Access Control &amp; Identity - All production access requires Multi-Factor Authentication (MFA) via FIDO2 WebAuthn hardware keys or TOTP.")</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Access_Control_Policy.md (quote: "1. Principle of Least Privilege - Role-Based Access Control (RBAC) and Just-in-Time (JIT) access are enforced across all production environm")</t>
+          <t>Access_Control_Policy.md (quote: "## 1. Principle of Least Privilege - Role-Based Access Control (RBAC) and Just-in-Time (JIT) access are enforced across all production envir")</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Access_Control_Policy.md (quote: "1. Principle of Least Privilege - Role-Based Access Control (RBAC) and Just-in-Time (JIT) access are enforced across all production environm")</t>
+          <t>Access_Control_Policy.md (quote: "## 1. Principle of Least Privilege - Role-Based Access Control (RBAC) and Just-in-Time (JIT) access are enforced across all production envir")</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "2. Encryption Standards - Data at Rest: Encrypted using AES-256 with AWS KMS customer-managed keys (CMKs) rotated annually. - Data in Transi")</t>
+          <t>Information_Security_Policy.md (quote: "## 2. Encryption Standards - Data at Rest: Encrypted using AES-256 with AWS KMS customer-managed keys (CMKs) rotated annually. - Data in Tra")</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "2. Encryption Standards - Data at Rest: Encrypted using AES-256 with AWS KMS customer-managed keys (CMKs) rotated annually. - Data in Transi")</t>
+          <t>Information_Security_Policy.md (quote: "## 2. Encryption Standards - Data at Rest: Encrypted using AES-256 with AWS KMS customer-managed keys (CMKs) rotated annually. - Data in Tra")</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "2. Encryption Standards - Data at Rest: Encrypted using AES-256 with AWS KMS customer-managed keys (CMKs) rotated annually. - Data in Transi")</t>
+          <t>Information_Security_Policy.md (quote: "## 2. Encryption Standards - Data at Rest: Encrypted using AES-256 with AWS KMS customer-managed keys (CMKs) rotated annually. - Data in Tra")</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "3. Vulnerability Management &amp; Penetration Testing - Third-party external penetration tests are conducted annually by independent CREST-certi")</t>
+          <t>Information_Security_Policy.md (quote: "## 3. Vulnerability Management &amp; Penetration Testing - Third-party external penetration tests are conducted annually by independent CREST-ce")</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "3. Vulnerability Management &amp; Penetration Testing - Third-party external penetration tests are conducted annually by independent CREST-certi")</t>
+          <t>Information_Security_Policy.md (quote: "## 3. Vulnerability Management &amp; Penetration Testing - Third-party external penetration tests are conducted annually by independent CREST-ce")</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "3. Vulnerability Management &amp; Penetration Testing - Third-party external penetration tests are conducted annually by independent CREST-certi")</t>
+          <t>Information_Security_Policy.md (quote: "## 3. Vulnerability Management &amp; Penetration Testing - Third-party external penetration tests are conducted annually by independent CREST-ce")</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "3. Vulnerability Management &amp; Penetration Testing - Third-party external penetration tests are conducted annually by independent CREST-certi")</t>
+          <t>Information_Security_Policy.md (quote: "## 3. Vulnerability Management &amp; Penetration Testing - Third-party external penetration tests are conducted annually by independent CREST-ce")</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "4. Employee Training &amp; Background Checks - All employees undergo standard criminal background checks prior to employment. - Security awarene")</t>
+          <t>Information_Security_Policy.md (quote: "## 4. Employee Training &amp; Background Checks - All employees undergo standard criminal background checks prior to employment. - Security awar")</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "4. Employee Training &amp; Background Checks - All employees undergo standard criminal background checks prior to employment. - Security awarene")</t>
+          <t>Information_Security_Policy.md (quote: "## 4. Employee Training &amp; Background Checks - All employees undergo standard criminal background checks prior to employment. - Security awar")</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Incident_Response_Plan.md (quote: "2. Customer Notification SLA - In the event of a confirmed security breach involving unauthorized access to Customer Personal Data, Northwin")</t>
+          <t>Incident_Response_Plan.md (quote: "## 2. Customer Notification SLA - In the event of a confirmed security breach involving unauthorized access to Customer Personal Data, North")</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Incident_Response_Plan.md (quote: "2. Customer Notification SLA - In the event of a confirmed security breach involving unauthorized access to Customer Personal Data, Northwin")</t>
+          <t>Incident_Response_Plan.md (quote: "## 2. Customer Notification SLA - In the event of a confirmed security breach involving unauthorized access to Customer Personal Data, North")</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Business_Continuity_and_Disaster_Recovery.md (quote: "1. High Availability Architecture - Multi-Region redundancy deployed across AWS us-east-1 and us-west-2 with automated failover. - Recovery ")</t>
+          <t>Business_Continuity_and_Disaster_Recovery.md (quote: "## 1. High Availability Architecture - Multi-Region redundancy deployed across AWS us-east-1 and us-west-2 with automated failover. - Recove")</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Business_Continuity_and_Disaster_Recovery.md (quote: "1. High Availability Architecture - Multi-Region redundancy deployed across AWS us-east-1 and us-west-2 with automated failover. - Recovery ")</t>
+          <t>Business_Continuity_and_Disaster_Recovery.md (quote: "## 1. High Availability Architecture - Multi-Region redundancy deployed across AWS us-east-1 and us-west-2 with automated failover. - Recove")</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Business_Continuity_and_Disaster_Recovery.md (quote: "1. High Availability Architecture - Multi-Region redundancy deployed across AWS us-east-1 and us-west-2 with automated failover. - Recovery ")</t>
+          <t>Business_Continuity_and_Disaster_Recovery.md (quote: "## 1. High Availability Architecture - Multi-Region redundancy deployed across AWS us-east-1 and us-west-2 with automated failover. - Recove")</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data_Retention_Policy.md (quote: "2. Retention Schedules - **Audit and Access Logs:** Retained for exactly 30 days in hot storage (Elasticsearch/OpenSearch) and archived to e")</t>
+          <t>Data_Retention_Policy.md (quote: "## 2. Retention Schedules - **Audit and Access Logs:** Retained for exactly 30 days in hot storage (Elasticsearch/OpenSearch) and archived t")</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data_Retention_Policy.md (quote: "2. Retention Schedules - **Audit and Access Logs:** Retained for exactly 30 days in hot storage (Elasticsearch/OpenSearch) and archived to e")</t>
+          <t>Data_Retention_Policy.md (quote: "## 2. Retention Schedules - **Audit and Access Logs:** Retained for exactly 30 days in hot storage (Elasticsearch/OpenSearch) and archived t")</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Access_Control_Policy.md (quote: "1. Principle of Least Privilege - Role-Based Access Control (RBAC) and Just-in-Time (JIT) access are enforced across all production environm")</t>
+          <t>Access_Control_Policy.md (quote: "## 1. Principle of Least Privilege - Role-Based Access Control (RBAC) and Just-in-Time (JIT) access are enforced across all production envir")</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data_Retention_Policy.md (quote: "2. Retention Schedules - **Audit and Access Logs:** Retained for exactly 30 days in hot storage (Elasticsearch/OpenSearch) and archived to e")</t>
+          <t>Data_Retention_Policy.md (quote: "## 2. Retention Schedules - **Audit and Access Logs:** Retained for exactly 30 days in hot storage (Elasticsearch/OpenSearch) and archived t")</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data_Retention_Policy.md (quote: "2. Retention Schedules - **Audit and Access Logs:** Retained for exactly 30 days in hot storage (Elasticsearch/OpenSearch) and archived to e")</t>
+          <t>Data_Retention_Policy.md (quote: "## 2. Retention Schedules - **Audit and Access Logs:** Retained for exactly 30 days in hot storage (Elasticsearch/OpenSearch) and archived t")</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Security_Questionnaire_SOP.md (quote: "1. Precedence of Information Sources 1. Current Policy Documents with effective date 2024 or later are the primary source of truth. 2. If co")</t>
+          <t>Security_Questionnaire_SOP.md (quote: "## 1. Precedence of Information Sources 1. Current Policy Documents with effective date 2024 or later are the primary source of truth. 2. If")</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Security_Questionnaire_SOP.md (quote: "2. Mandatory Escalation Categories (DO NOT AUTO-ANSWER) Any question touching the following categories must be escalated to a human for sign")</t>
+          <t>Security_Questionnaire_SOP.md (quote: "## 2. Mandatory Escalation Categories (DO NOT AUTO-ANSWER) Any question touching the following categories must be escalated to a human for s")</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Information_Security_Policy.md (quote: "1. Access Control &amp; Identity - All production access requires Multi-Factor Authentication (MFA) via FIDO2 WebAuthn hardware keys or TOTP. SM")</t>
+          <t>Information_Security_Policy.md (quote: "## 1. Access Control &amp; Identity - All production access requires Multi-Factor Authentication (MFA) via FIDO2 WebAuthn hardware keys or TOTP.")</t>
         </is>
       </c>
     </row>
